--- a/www/terminologies/ASS-X02-TranscoSectActADELI-SectAct.xlsx
+++ b/www/terminologies/ASS-X02-TranscoSectActADELI-SectAct.xlsx
@@ -99,13 +99,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_G19-SecteurActiviteADELI/FHIR/TRE-G19-SecteurActiviteADELI|20250523120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_G19-SecteurActiviteADELI/FHIR/TRE-G19-SecteurActiviteADELI</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R02-SecteurActivite/FHIR/TRE-R02-SecteurActivite|20250523120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R02-SecteurActivite/FHIR/TRE-R02-SecteurActivite</t>
   </si>
   <si>
     <t>10</t>
